--- a/projetogustavo/Gerador de Grafico/graficos_excel_melhorados.xlsx
+++ b/projetogustavo/Gerador de Grafico/graficos_excel_melhorados.xlsx
@@ -317,20 +317,101 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Valores</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Pergunta_Q1  A cidade que voc'!$A$2:$A$4</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
+            <c:v>Capital</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q1  A cidade que voc'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Capital</c:v>
                 </c:pt>
-                <c:pt idx="1">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q1  A cidade que voc'!$B$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>46</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Região metropolitana</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC107"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q1  A cidade que voc'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Região metropolitana</c:v>
                 </c:pt>
-                <c:pt idx="2">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q1  A cidade que voc'!$B$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>21.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Interior do estado</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2196F3"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q1  A cidade que voc'!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Interior do estado</c:v>
                 </c:pt>
               </c:strCache>
@@ -338,17 +419,11 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pergunta_Q1  A cidade que voc'!$B$2:$B$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>46</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>21.5</c:v>
-                </c:pt>
-                <c:pt idx="2">
+              <c:f>'Pergunta_Q1  A cidade que voc'!$B$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>32.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -466,17 +541,62 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Valores</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Pergunta_Q5  Observe as image'!$A$2:$A$3</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
+            <c:v>Sim</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q5  Observe as image'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Sim</c:v>
                 </c:pt>
-                <c:pt idx="1">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q5  Observe as image'!$B$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>45.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Não</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC107"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q5  Observe as image'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Não</c:v>
                 </c:pt>
               </c:strCache>
@@ -484,14 +604,11 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pergunta_Q5  Observe as image'!$B$2:$B$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>45.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
+              <c:f>'Pergunta_Q5  Observe as image'!$B$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>54.50000000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -609,17 +726,62 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Valores</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Pergunta_Q6  Observe as image'!$A$2:$A$3</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
+            <c:v>Sim</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q6  Observe as image'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Sim</c:v>
                 </c:pt>
-                <c:pt idx="1">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q6  Observe as image'!$B$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>68</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Não</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC107"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q6  Observe as image'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Não</c:v>
                 </c:pt>
               </c:strCache>
@@ -627,14 +789,11 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pergunta_Q6  Observe as image'!$B$2:$B$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>68</c:v>
-                </c:pt>
-                <c:pt idx="1">
+              <c:f>'Pergunta_Q6  Observe as image'!$B$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>32</c:v>
                 </c:pt>
               </c:numCache>
@@ -752,27 +911,184 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Valores</c:v>
-          </c:tx>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Pergunta_Q7  Em qual ano nós '!$A$2:$A$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+            <c:v>2021</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Pergunta_Q7  Em qual ano nós '!$A$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>2021</c:v>
                 </c:pt>
-                <c:pt idx="1">
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q7  Em qual ano nós '!$B$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>2022</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC107"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Pergunta_Q7  Em qual ano nós '!$A$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="2">
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q7  Em qual ano nós '!$B$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>2023</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2196F3"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Pergunta_Q7  Em qual ano nós '!$A$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>2023</c:v>
                 </c:pt>
-                <c:pt idx="3">
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q7  Em qual ano nós '!$B$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>2024</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF5722"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Pergunta_Q7  Em qual ano nós '!$A$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>2024</c:v>
                 </c:pt>
-                <c:pt idx="4">
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q7  Em qual ano nós '!$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>2025</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="9C27B0"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Pergunta_Q7  Em qual ano nós '!$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
@@ -780,23 +1096,11 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pergunta_Q7  Em qual ano nós '!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
+              <c:f>'Pergunta_Q7  Em qual ano nós '!$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -916,26 +1220,179 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Valores</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Pergunta_Q8  Você costuma com'!$A$2:$A$6</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
+            <c:v>Mercados</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q8  Você costuma com'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Mercados</c:v>
                 </c:pt>
-                <c:pt idx="1">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q8  Você costuma com'!$B$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>84.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Internet</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC107"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q8  Você costuma com'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Internet</c:v>
                 </c:pt>
-                <c:pt idx="2">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q8  Você costuma com'!$B$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Lojas especializadas</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2196F3"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q8  Você costuma com'!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Lojas especializadas</c:v>
                 </c:pt>
-                <c:pt idx="3">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q8  Você costuma com'!$B$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>23.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>Outros</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF5722"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q8  Você costuma com'!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Outros</c:v>
                 </c:pt>
-                <c:pt idx="4">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q8  Você costuma com'!$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>Não compro esse tipo de produto</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="9C27B0"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q8  Você costuma com'!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Não compro esse tipo de produto</c:v>
                 </c:pt>
               </c:strCache>
@@ -943,23 +1400,11 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pergunta_Q8  Você costuma com'!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>84.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>23.5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
+              <c:f>'Pergunta_Q8  Você costuma com'!$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
@@ -1077,17 +1522,62 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Valores</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Pergunta_Q9  Esse tipo de pro'!$A$2:$A$3</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
+            <c:v>Sim</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q9  Esse tipo de pro'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Sim</c:v>
                 </c:pt>
-                <c:pt idx="1">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q9  Esse tipo de pro'!$B$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>91.14583333333334</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Não</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC107"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q9  Esse tipo de pro'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Não</c:v>
                 </c:pt>
               </c:strCache>
@@ -1095,14 +1585,11 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pergunta_Q9  Esse tipo de pro'!$B$2:$B$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>91.14583333333334</c:v>
-                </c:pt>
-                <c:pt idx="1">
+              <c:f>'Pergunta_Q9  Esse tipo de pro'!$B$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>8.854166666666668</c:v>
                 </c:pt>
               </c:numCache>
@@ -1220,17 +1707,62 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Valores</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Pergunta_Q10  Quando você com'!$A$2:$A$3</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
+            <c:v>A marca</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q10  Quando você com'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>A marca</c:v>
                 </c:pt>
-                <c:pt idx="1">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q10  Quando você com'!$B$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>52.60416666666666</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>O preço</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC107"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q10  Quando você com'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>O preço</c:v>
                 </c:pt>
               </c:strCache>
@@ -1238,14 +1770,11 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pergunta_Q10  Quando você com'!$B$2:$B$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>52.60416666666666</c:v>
-                </c:pt>
-                <c:pt idx="1">
+              <c:f>'Pergunta_Q10  Quando você com'!$B$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>47.39583333333333</c:v>
                 </c:pt>
               </c:numCache>
@@ -1363,17 +1892,62 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Valores</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Pergunta_Q10.1  Você leva em '!$A$2:$A$3</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
+            <c:v>Sim</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q10.1  Você leva em '!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Sim</c:v>
                 </c:pt>
-                <c:pt idx="1">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q10.1  Você leva em '!$B$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>96.03960396039604</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Não</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC107"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q10.1  Você leva em '!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Não</c:v>
                 </c:pt>
               </c:strCache>
@@ -1381,14 +1955,11 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pergunta_Q10.1  Você leva em '!$B$2:$B$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>96.03960396039604</c:v>
-                </c:pt>
-                <c:pt idx="1">
+              <c:f>'Pergunta_Q10.1  Você leva em '!$B$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>3.96039603960396</c:v>
                 </c:pt>
               </c:numCache>
@@ -1506,26 +2077,179 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Valores</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Pergunta_Q11  Quando você est'!$A$2:$A$6</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
+            <c:v>Menos de 10 segundos</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q11  Quando você est'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Menos de 10 segundos</c:v>
                 </c:pt>
-                <c:pt idx="1">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q11  Quando você est'!$B$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>11.45833333333333</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>10 segundos a 1 minuto</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC107"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q11  Quando você est'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>10 segundos a 1 minuto</c:v>
                 </c:pt>
-                <c:pt idx="2">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q11  Quando você est'!$B$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>40.625</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>1 a 2 minutos</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2196F3"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q11  Quando você est'!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>1 a 2 minutos</c:v>
                 </c:pt>
-                <c:pt idx="3">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q11  Quando você est'!$B$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>28.125</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>2 a 5 minutos</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF5722"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q11  Quando você est'!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>2 a 5 minutos</c:v>
                 </c:pt>
-                <c:pt idx="4">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q11  Quando você est'!$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>11.45833333333333</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>Mais de 5 minutos</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="9C27B0"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q11  Quando você est'!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Mais de 5 minutos</c:v>
                 </c:pt>
               </c:strCache>
@@ -1533,23 +2257,11 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pergunta_Q11  Quando você est'!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>11.45833333333333</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>40.625</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>28.125</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>11.45833333333333</c:v>
-                </c:pt>
-                <c:pt idx="4">
+              <c:f>'Pergunta_Q11  Quando você est'!$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>8.333333333333332</c:v>
                 </c:pt>
               </c:numCache>
@@ -1667,17 +2379,62 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Valores</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Pergunta_sexoHU  Sexo'!$A$2:$A$3</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
+            <c:v>Masculino</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_sexoHU  Sexo'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Masculino</c:v>
                 </c:pt>
-                <c:pt idx="1">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_sexoHU  Sexo'!$B$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>48</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Feminino</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC107"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_sexoHU  Sexo'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Feminino</c:v>
                 </c:pt>
               </c:strCache>
@@ -1685,14 +2442,11 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pergunta_sexoHU  Sexo'!$B$2:$B$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>48</c:v>
-                </c:pt>
-                <c:pt idx="1">
+              <c:f>'Pergunta_sexoHU  Sexo'!$B$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>52</c:v>
                 </c:pt>
               </c:numCache>
@@ -1810,26 +2564,179 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Valores</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Pergunta_FaixaEtária  Faixa E'!$A$2:$A$6</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
+            <c:v>De 16 a 24 anos</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_FaixaEtária  Faixa E'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>De 16 a 24 anos</c:v>
                 </c:pt>
-                <c:pt idx="1">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_FaixaEtária  Faixa E'!$B$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>18</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>De 25 a 29 anos</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC107"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_FaixaEtária  Faixa E'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>De 25 a 29 anos</c:v>
                 </c:pt>
-                <c:pt idx="2">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_FaixaEtária  Faixa E'!$B$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>De 30 a 39 anos</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2196F3"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_FaixaEtária  Faixa E'!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>De 30 a 39 anos</c:v>
                 </c:pt>
-                <c:pt idx="3">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_FaixaEtária  Faixa E'!$B$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>De 40 a 49 anos</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF5722"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_FaixaEtária  Faixa E'!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>De 40 a 49 anos</c:v>
                 </c:pt>
-                <c:pt idx="4">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_FaixaEtária  Faixa E'!$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>18</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>50 anos ou mais</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="9C27B0"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_FaixaEtária  Faixa E'!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>50 anos ou mais</c:v>
                 </c:pt>
               </c:strCache>
@@ -1837,23 +2744,11 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pergunta_FaixaEtária  Faixa E'!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="4">
+              <c:f>'Pergunta_FaixaEtária  Faixa E'!$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>34</c:v>
                 </c:pt>
               </c:numCache>
@@ -1971,32 +2866,257 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Valores</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Pergunta_rfHU  Renda Familiar'!$A$2:$A$8</c:f>
-              <c:strCache>
-                <c:ptCount val="7"/>
+            <c:v>Até R$ 1.320</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_rfHU  Renda Familiar'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Até R$ 1.320</c:v>
                 </c:pt>
-                <c:pt idx="1">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_rfHU  Renda Familiar'!$B$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>De R$ 1.321 a R$ 2.640</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC107"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_rfHU  Renda Familiar'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>De R$ 1.321 a R$ 2.640</c:v>
                 </c:pt>
-                <c:pt idx="2">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_rfHU  Renda Familiar'!$B$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>De R$ 2.641 a R$ 3.960</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2196F3"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_rfHU  Renda Familiar'!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>De R$ 2.641 a R$ 3.960</c:v>
                 </c:pt>
-                <c:pt idx="3">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_rfHU  Renda Familiar'!$B$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>26.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>De R$ 3.961 a R$ 6.600</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF5722"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_rfHU  Renda Familiar'!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>De R$ 3.961 a R$ 6.600</c:v>
                 </c:pt>
-                <c:pt idx="4">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_rfHU  Renda Familiar'!$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>20.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>De R$ 6.601 a R$ 13.200</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="9C27B0"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_rfHU  Renda Familiar'!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>De R$ 6.601 a R$ 13.200</c:v>
                 </c:pt>
-                <c:pt idx="5">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_rfHU  Renda Familiar'!$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>13.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:v>De R$ 13.201 a R$ 19.800</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="E91E63"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_rfHU  Renda Familiar'!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>De R$ 13.201 a R$ 19.800</c:v>
                 </c:pt>
-                <c:pt idx="6">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_rfHU  Renda Familiar'!$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>8.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:v>Mais de R$ 19.800</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="00BCD4"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_rfHU  Renda Familiar'!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Mais de R$ 19.800</c:v>
                 </c:pt>
               </c:strCache>
@@ -2004,29 +3124,11 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pergunta_rfHU  Renda Familiar'!$B$2:$B$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>26.5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>20.5</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>13.5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>8.5</c:v>
-                </c:pt>
-                <c:pt idx="6">
+              <c:f>'Pergunta_rfHU  Renda Familiar'!$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
@@ -2144,92 +3246,1037 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Valores</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Pergunta_Estado'!$A$2:$A$28</c:f>
-              <c:strCache>
-                <c:ptCount val="27"/>
+            <c:v>Acre</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Acre</c:v>
                 </c:pt>
-                <c:pt idx="1">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Alagoas</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC107"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Alagoas</c:v>
                 </c:pt>
-                <c:pt idx="2">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Amapá</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2196F3"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Amapá</c:v>
                 </c:pt>
-                <c:pt idx="3">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>Amazonas</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF5722"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Amazonas</c:v>
                 </c:pt>
-                <c:pt idx="4">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>Bahia</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="9C27B0"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Bahia</c:v>
                 </c:pt>
-                <c:pt idx="5">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>6.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:v>Ceará</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="E91E63"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Ceará</c:v>
                 </c:pt>
-                <c:pt idx="6">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:v>Distrito Federal</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="00BCD4"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Distrito Federal</c:v>
                 </c:pt>
-                <c:pt idx="7">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:v>Espírito Santo</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="8BC34A"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Espírito Santo</c:v>
                 </c:pt>
-                <c:pt idx="8">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:v>Goiás</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Goiás</c:v>
                 </c:pt>
-                <c:pt idx="9">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:v>Maranhão</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC107"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Maranhão</c:v>
                 </c:pt>
-                <c:pt idx="10">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:v>Mato Grosso</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2196F3"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Mato Grosso</c:v>
                 </c:pt>
-                <c:pt idx="11">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:v>Mato Grosso do Sul</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF5722"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Mato Grosso do Sul</c:v>
                 </c:pt>
-                <c:pt idx="12">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="12"/>
+          <c:order val="12"/>
+          <c:tx>
+            <c:v>Minas Gerais</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="9C27B0"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Minas Gerais</c:v>
                 </c:pt>
-                <c:pt idx="13">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="13"/>
+          <c:order val="13"/>
+          <c:tx>
+            <c:v>Pará</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="E91E63"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Pará</c:v>
                 </c:pt>
-                <c:pt idx="14">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="14"/>
+          <c:order val="14"/>
+          <c:tx>
+            <c:v>Paraíba</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="00BCD4"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Paraíba</c:v>
                 </c:pt>
-                <c:pt idx="15">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="15"/>
+          <c:order val="15"/>
+          <c:tx>
+            <c:v>Paraná</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="8BC34A"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Paraná</c:v>
                 </c:pt>
-                <c:pt idx="16">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="16"/>
+          <c:order val="16"/>
+          <c:tx>
+            <c:v>Pernambuco</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$18</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Pernambuco</c:v>
                 </c:pt>
-                <c:pt idx="17">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="17"/>
+          <c:order val="17"/>
+          <c:tx>
+            <c:v>Piauí</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC107"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Piauí</c:v>
                 </c:pt>
-                <c:pt idx="18">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="18"/>
+          <c:order val="18"/>
+          <c:tx>
+            <c:v>Rio de Janeiro</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2196F3"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Rio de Janeiro</c:v>
                 </c:pt>
-                <c:pt idx="19">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>12.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="19"/>
+          <c:order val="19"/>
+          <c:tx>
+            <c:v>Rio Grande do Norte</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF5722"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Rio Grande do Norte</c:v>
                 </c:pt>
-                <c:pt idx="20">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="20"/>
+          <c:order val="20"/>
+          <c:tx>
+            <c:v>Rio Grande do Sul</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="9C27B0"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Rio Grande do Sul</c:v>
                 </c:pt>
-                <c:pt idx="21">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="21"/>
+          <c:order val="21"/>
+          <c:tx>
+            <c:v>Rondônia</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="E91E63"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$23</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Rondônia</c:v>
                 </c:pt>
-                <c:pt idx="22">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="22"/>
+          <c:order val="22"/>
+          <c:tx>
+            <c:v>Roraima</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="00BCD4"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$24</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Roraima</c:v>
                 </c:pt>
-                <c:pt idx="23">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="23"/>
+          <c:order val="23"/>
+          <c:tx>
+            <c:v>Santa Catarina</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="8BC34A"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$25</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Santa Catarina</c:v>
                 </c:pt>
-                <c:pt idx="24">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="24"/>
+          <c:order val="24"/>
+          <c:tx>
+            <c:v>São Paulo</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$26</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>São Paulo</c:v>
                 </c:pt>
-                <c:pt idx="25">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="25"/>
+          <c:order val="25"/>
+          <c:tx>
+            <c:v>Sergipe</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC107"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Sergipe</c:v>
                 </c:pt>
-                <c:pt idx="26">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Estado'!$B$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="26"/>
+          <c:order val="26"/>
+          <c:tx>
+            <c:v>Tocantins</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2196F3"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Estado'!$A$28</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Tocantins</c:v>
                 </c:pt>
               </c:strCache>
@@ -2237,89 +4284,11 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pergunta_Estado'!$B$2:$B$28</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>6.5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>3.5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.5</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2.5</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.5</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>4.5</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>4.5</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>12.5</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>3.5</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1.5</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1.5</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>4.5</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="26">
+              <c:f>'Pergunta_Estado'!$B$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2437,17 +4406,62 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Valores</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Pergunta_Q1  Você conhece a m'!$A$2:$A$3</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
+            <c:v>Sim</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q1  Você conhece a m'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Sim</c:v>
                 </c:pt>
-                <c:pt idx="1">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q1  Você conhece a m'!$B$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>44</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Não</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC107"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q1  Você conhece a m'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Não</c:v>
                 </c:pt>
               </c:strCache>
@@ -2455,14 +4469,11 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pergunta_Q1  Você conhece a m'!$B$2:$B$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>44</c:v>
-                </c:pt>
-                <c:pt idx="1">
+              <c:f>'Pergunta_Q1  Você conhece a m'!$B$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>56.00000000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -2580,17 +4591,62 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Valores</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Pergunta_Q2  Você conhece a m'!$A$2:$A$3</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
+            <c:v>Sim</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q2  Você conhece a m'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Sim</c:v>
                 </c:pt>
-                <c:pt idx="1">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q2  Você conhece a m'!$B$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>21</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Não</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC107"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q2  Você conhece a m'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Não</c:v>
                 </c:pt>
               </c:strCache>
@@ -2598,14 +4654,11 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pergunta_Q2  Você conhece a m'!$B$2:$B$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="1">
+              <c:f>'Pergunta_Q2  Você conhece a m'!$B$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>79</c:v>
                 </c:pt>
               </c:numCache>
@@ -2723,17 +4776,62 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Valores</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Pergunta_Q3  Você considera e'!$A$2:$A$3</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
+            <c:v>Sim</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q3  Você considera e'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Sim</c:v>
                 </c:pt>
-                <c:pt idx="1">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q3  Você considera e'!$B$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>66.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Não</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC107"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q3  Você considera e'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>Não</c:v>
                 </c:pt>
               </c:strCache>
@@ -2741,14 +4839,11 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pergunta_Q3  Você considera e'!$B$2:$B$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>66.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
+              <c:f>'Pergunta_Q3  Você considera e'!$B$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>33.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2866,26 +4961,179 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Valores</c:v>
-          </c:tx>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Pergunta_Q4  Observe as image'!$A$2:$A$6</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
+            <c:v>1- Muito Dessemelhantes</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q4  Observe as image'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>1- Muito Dessemelhantes</c:v>
                 </c:pt>
-                <c:pt idx="1">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q4  Observe as image'!$B$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>13.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>2- Dessemelhantes</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC107"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q4  Observe as image'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>2- Dessemelhantes</c:v>
                 </c:pt>
-                <c:pt idx="2">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q4  Observe as image'!$B$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>23</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>3 – Não sei responder</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2196F3"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q4  Observe as image'!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>3 – Não sei responder</c:v>
                 </c:pt>
-                <c:pt idx="3">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q4  Observe as image'!$B$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>4 – Semelhantes</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF5722"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q4  Observe as image'!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>4 – Semelhantes</c:v>
                 </c:pt>
-                <c:pt idx="4">
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pergunta_Q4  Observe as image'!$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>47.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>5 – Muito Semelhantes</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="9C27B0"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pergunta_Q4  Observe as image'!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>5 – Muito Semelhantes</c:v>
                 </c:pt>
               </c:strCache>
@@ -2893,23 +5141,11 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pergunta_Q4  Observe as image'!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>13.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>47.5</c:v>
-                </c:pt>
-                <c:pt idx="4">
+              <c:f>'Pergunta_Q4  Observe as image'!$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
